--- a/Employee_Reports_wi48/Roshan Chaminda Udawaththa Udawaththa Kankanamge Q0580.xlsx
+++ b/Employee_Reports_wi48/Roshan Chaminda Udawaththa Udawaththa Kankanamge Q0580.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-30</v>
+        <v>-33</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-59</v>
+        <v>-62</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-48</v>
+        <v>-51</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-34</v>
+        <v>-37</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-322</v>
+        <v>-325</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-402</v>
+        <v>-405</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-425</v>
+        <v>-428</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-335</v>
+        <v>-338</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-335</v>
+        <v>-338</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1365,9 +1365,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>17-Mar-2025</t>
@@ -1379,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1416,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
